--- a/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.28951136394964</v>
+        <v>45.81260608810479</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1719449861628</v>
+        <v>98.67497568998047</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03364568127407</v>
+        <v>88.08835848083173</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91952848058432</v>
+        <v>45.94807634028534</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228753812948348</v>
+        <v>2.228872424516733</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701509251549873</v>
+        <v>5.720793964223981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429179376494495</v>
+        <v>0.7429574748389109</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9698707436409</v>
+        <v>33.97920960077526</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17422513187467</v>
+        <v>34.1760438425899</v>
       </c>
       <c r="I3" t="n">
-        <v>6.573131693301756</v>
+        <v>6.596996956143755</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643237110309059</v>
+        <v>4.643484217743193</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96635431872594</v>
+        <v>11.91164151916827</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87817793615136</v>
+        <v>48.90349884569005</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640607354616</v>
+        <v>106.7632167051437</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12694295336277</v>
+        <v>87.35208628472819</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64928397528031</v>
+        <v>42.85181084549352</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185103638158673</v>
+        <v>2.194336712077346</v>
       </c>
       <c r="E4" t="n">
-        <v>6.504697273802487</v>
+        <v>6.550327725400022</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444780981642027</v>
+        <v>0.7445193506206323</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30457034710179</v>
+        <v>33.45271189781926</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24599251555333</v>
+        <v>34.24789012854908</v>
       </c>
       <c r="I4" t="n">
-        <v>5.489112967056027</v>
+        <v>5.509054528882889</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652988113526267</v>
+        <v>4.653245941378952</v>
       </c>
       <c r="K4" t="n">
-        <v>12.87305704663722</v>
+        <v>12.64791371527181</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29507198660186</v>
+        <v>44.31702552378622</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8174130085194</v>
+        <v>99.81675008455156</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.92307406106747</v>
+        <v>86.43446431207759</v>
       </c>
       <c r="C5" t="n">
-        <v>42.29735726591185</v>
+        <v>42.78942017561153</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126235551931837</v>
+        <v>2.150426035427566</v>
       </c>
       <c r="E5" t="n">
-        <v>7.093188665709295</v>
+        <v>7.185753231158263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458015652717545</v>
+        <v>0.74583983479465</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40732397182548</v>
+        <v>32.78329265731775</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3068720025007</v>
+        <v>34.3086324005539</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582392520879931</v>
+        <v>4.599021185358906</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661259782948465</v>
+        <v>4.661498967466562</v>
       </c>
       <c r="K5" t="n">
-        <v>14.07692593893253</v>
+        <v>13.5655356879224</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47324143495962</v>
+        <v>43.49201484399711</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84752463980399</v>
+        <v>99.84697070753103</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.667146731673</v>
+        <v>85.37838010080337</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75306583102165</v>
+        <v>42.44798048983495</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065189364321316</v>
+        <v>2.099648922989296</v>
       </c>
       <c r="E6" t="n">
-        <v>7.526938340155747</v>
+        <v>7.655789171849896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469244923717212</v>
+        <v>0.7469574978354222</v>
       </c>
       <c r="G6" t="n">
-        <v>31.47687975206746</v>
+        <v>32.00919445076104</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35852664909918</v>
+        <v>34.36004490042941</v>
       </c>
       <c r="I6" t="n">
-        <v>3.824410056334325</v>
+        <v>3.83826079546691</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668278077323257</v>
+        <v>4.668484361471388</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33285326832701</v>
+        <v>14.62161989919663</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78679221951577</v>
+        <v>42.80264902248621</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87271131886443</v>
+        <v>99.8722494115178</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.09932985048121</v>
+        <v>84.05930291085444</v>
       </c>
       <c r="C7" t="n">
-        <v>40.77928313110422</v>
+        <v>41.7256046306349</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98889296922656</v>
+        <v>2.035916761394554</v>
       </c>
       <c r="E7" t="n">
-        <v>7.780710961353652</v>
+        <v>7.957176262587923</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478805777669862</v>
+        <v>0.7479061200315651</v>
       </c>
       <c r="G7" t="n">
-        <v>30.31399730874096</v>
+        <v>31.03759623216503</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40250657728136</v>
+        <v>34.40368152145199</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191087845068005</v>
+        <v>3.20261276302611</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674253611043664</v>
+        <v>4.674413250197282</v>
       </c>
       <c r="K7" t="n">
-        <v>16.9006701495188</v>
+        <v>15.94069708914556</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21381310670104</v>
+        <v>42.22707992478989</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89376638732406</v>
+        <v>99.89338164457035</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.90549665227292</v>
+        <v>88.92716254395577</v>
       </c>
       <c r="C8" t="n">
-        <v>43.05488828813161</v>
+        <v>44.05058549541766</v>
       </c>
       <c r="D8" t="n">
-        <v>1.993115960665474</v>
+        <v>2.040208098899428</v>
       </c>
       <c r="E8" t="n">
-        <v>9.59373097511032</v>
+        <v>9.804204691191716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494685431960504</v>
+        <v>0.7494825683637736</v>
       </c>
       <c r="G8" t="n">
-        <v>30.8099907122131</v>
+        <v>31.54954065680356</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47555298701831</v>
+        <v>34.47619814473358</v>
       </c>
       <c r="I8" t="n">
-        <v>5.599459079094339</v>
+        <v>5.623262331690123</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684178394975315</v>
+        <v>4.684266052273586</v>
       </c>
       <c r="K8" t="n">
-        <v>12.09450334772709</v>
+        <v>11.07283745604422</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66435519717949</v>
+        <v>44.68952923315461</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81374683303818</v>
+        <v>99.81295218461651</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.83069926094213</v>
+        <v>87.08542979775436</v>
       </c>
       <c r="C9" t="n">
-        <v>41.84921144972837</v>
+        <v>43.08271192623626</v>
       </c>
       <c r="D9" t="n">
-        <v>1.899019108521307</v>
+        <v>1.957127701140062</v>
       </c>
       <c r="E9" t="n">
-        <v>9.919916586616031</v>
+        <v>10.18737450301231</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508291795360921</v>
+        <v>0.7508293015335434</v>
       </c>
       <c r="G9" t="n">
-        <v>29.35542248947793</v>
+        <v>30.2647950525162</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53814225866023</v>
+        <v>34.53814787054299</v>
       </c>
       <c r="I9" t="n">
-        <v>4.674687266029963</v>
+        <v>4.694472234424615</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692682372100575</v>
+        <v>4.692683134584647</v>
       </c>
       <c r="K9" t="n">
-        <v>14.16930073905788</v>
+        <v>12.91457020224563</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8259472812389</v>
+        <v>43.84651614008227</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84445947002514</v>
+        <v>99.84379826856416</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.54613083009345</v>
+        <v>84.97457365831912</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28988105358462</v>
+        <v>41.70128045132583</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796443751473631</v>
+        <v>1.862573049931242</v>
       </c>
       <c r="E10" t="n">
-        <v>10.03436594192028</v>
+        <v>10.34820433312144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519979800493498</v>
+        <v>0.7519832953266544</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76979181855317</v>
+        <v>28.80261292795166</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59190708227008</v>
+        <v>34.59123158502609</v>
       </c>
       <c r="I10" t="n">
-        <v>3.901636880518493</v>
+        <v>3.918072871170432</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699987375308435</v>
+        <v>4.699895595791591</v>
       </c>
       <c r="K10" t="n">
-        <v>16.45386916990655</v>
+        <v>15.02542634168089</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12639735245244</v>
+        <v>43.14289120048149</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87014757594362</v>
+        <v>99.86959799348821</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.15607207953975</v>
+        <v>82.6505728469383</v>
       </c>
       <c r="C11" t="n">
-        <v>38.50443475262585</v>
+        <v>39.98554958261276</v>
       </c>
       <c r="D11" t="n">
-        <v>1.690278261444219</v>
+        <v>1.759348122996165</v>
       </c>
       <c r="E11" t="n">
-        <v>9.983977776572299</v>
+        <v>10.31959489077586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530035686980394</v>
+        <v>0.752974822441235</v>
       </c>
       <c r="G11" t="n">
-        <v>26.1286641439388</v>
+        <v>27.20635466836992</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6381641601098</v>
+        <v>34.6368418322968</v>
       </c>
       <c r="I11" t="n">
-        <v>3.255711864413861</v>
+        <v>3.269365869800597</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706272304362745</v>
+        <v>4.70609264025772</v>
       </c>
       <c r="K11" t="n">
-        <v>18.84392792046026</v>
+        <v>17.34942715306169</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54325852467726</v>
+        <v>42.55618790679304</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89162119776336</v>
+        <v>99.89116464246749</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.69766593596131</v>
+        <v>80.28165257967922</v>
       </c>
       <c r="C12" t="n">
-        <v>36.5496998104657</v>
+        <v>38.12343083035195</v>
       </c>
       <c r="D12" t="n">
-        <v>1.58217396440295</v>
+        <v>1.65513098516872</v>
       </c>
       <c r="E12" t="n">
-        <v>9.798139843109668</v>
+        <v>10.16289390083878</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538698880303483</v>
+        <v>0.7538275626328653</v>
       </c>
       <c r="G12" t="n">
-        <v>24.45756599735642</v>
+        <v>25.59475297499543</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67801484939601</v>
+        <v>34.67606788111179</v>
       </c>
       <c r="I12" t="n">
-        <v>2.716214593476229</v>
+        <v>2.727557008476207</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711686800189676</v>
+        <v>4.711422266455409</v>
       </c>
       <c r="K12" t="n">
-        <v>21.30233406403872</v>
+        <v>19.71834742032079</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05752968481742</v>
+        <v>42.06740603072169</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90956355932184</v>
+        <v>99.90918428139443</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.27066605669255</v>
+        <v>77.87716221675811</v>
       </c>
       <c r="C13" t="n">
-        <v>34.54200184050234</v>
+        <v>36.14094242300305</v>
       </c>
       <c r="D13" t="n">
-        <v>1.476487161985623</v>
+        <v>1.550265222737698</v>
       </c>
       <c r="E13" t="n">
-        <v>9.521264669617903</v>
+        <v>9.898189708365109</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546163888199997</v>
+        <v>0.7545616638678626</v>
       </c>
       <c r="G13" t="n">
-        <v>22.8238379729247</v>
+        <v>23.97312102622072</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71235388571998</v>
+        <v>34.70983653792167</v>
       </c>
       <c r="I13" t="n">
-        <v>2.265753547499324</v>
+        <v>2.275177658470916</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716352430124997</v>
+        <v>4.716010399174142</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72933394330746</v>
+        <v>22.12283778324189</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65321381081588</v>
+        <v>41.66045432129737</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92454959462569</v>
+        <v>99.92423452754232</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.1815426338693</v>
+        <v>84.52482874768205</v>
       </c>
       <c r="C14" t="n">
-        <v>38.95637616421676</v>
+        <v>40.06323481317646</v>
       </c>
       <c r="D14" t="n">
-        <v>1.478112233622869</v>
+        <v>1.552257739693079</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9531205999954</v>
+        <v>12.12855229199481</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755446945103891</v>
+        <v>0.7555314830233759</v>
       </c>
       <c r="G14" t="n">
-        <v>24.8125730888106</v>
+        <v>25.67838556796969</v>
       </c>
       <c r="H14" t="n">
-        <v>36.71417390374133</v>
+        <v>36.42890071046181</v>
       </c>
       <c r="I14" t="n">
-        <v>2.746572455695889</v>
+        <v>3.259129185643176</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721543406899318</v>
+        <v>4.722071768896099</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8184573661307</v>
+        <v>15.47517125231796</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13371470935873</v>
+        <v>44.35309574498216</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90854823970619</v>
+        <v>99.89150181047658</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.34393512756</v>
+        <v>83.75206567723824</v>
       </c>
       <c r="C15" t="n">
-        <v>38.5431137578479</v>
+        <v>39.7892114137261</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44707969637062</v>
+        <v>1.522787351500838</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08399046720465</v>
+        <v>12.35684761261368</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561475343752266</v>
+        <v>0.7563490546586539</v>
       </c>
       <c r="G15" t="n">
-        <v>24.29164031984527</v>
+        <v>25.19628388084782</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74822203446661</v>
+        <v>36.47373623861647</v>
       </c>
       <c r="I15" t="n">
-        <v>2.290932985452461</v>
+        <v>2.718879947384201</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725922089845167</v>
+        <v>4.727181591616587</v>
       </c>
       <c r="K15" t="n">
-        <v>17.65606487244</v>
+        <v>16.24793432276175</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72452769038722</v>
+        <v>43.8723228972443</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92370632067511</v>
+        <v>99.90946863373215</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.86818340194449</v>
+        <v>81.25532418570592</v>
       </c>
       <c r="C16" t="n">
-        <v>36.42129142904864</v>
+        <v>37.71314862300315</v>
       </c>
       <c r="D16" t="n">
-        <v>1.353436947309807</v>
+        <v>1.426815595915087</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62045575100442</v>
+        <v>11.95604637976836</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567504947769776</v>
+        <v>0.7570527129730962</v>
       </c>
       <c r="G16" t="n">
-        <v>22.71969097631431</v>
+        <v>23.60831981226093</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77752547290188</v>
+        <v>36.50766904729124</v>
       </c>
       <c r="I16" t="n">
-        <v>1.910633167280976</v>
+        <v>2.267841181415351</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729690592356111</v>
+        <v>4.731579456081851</v>
       </c>
       <c r="K16" t="n">
-        <v>20.13181659805552</v>
+        <v>18.74467581429407</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38325494552217</v>
+        <v>43.46665111971988</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93636297262633</v>
+        <v>99.9244755570171</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.55397183733781</v>
+        <v>82.78949150565538</v>
       </c>
       <c r="C17" t="n">
-        <v>37.66064350614421</v>
+        <v>38.81326523445603</v>
       </c>
       <c r="D17" t="n">
-        <v>1.354474797170021</v>
+        <v>1.428149904917313</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39132947572792</v>
+        <v>12.69379535255929</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573307902955699</v>
+        <v>0.7577606827016103</v>
       </c>
       <c r="G17" t="n">
-        <v>23.18638758185415</v>
+        <v>23.96985612854035</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25500198333214</v>
+        <v>36.88126839249776</v>
       </c>
       <c r="I17" t="n">
-        <v>1.876129769610683</v>
+        <v>2.322656777553992</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733317439347313</v>
+        <v>4.736004266885065</v>
       </c>
       <c r="K17" t="n">
-        <v>18.44602816266219</v>
+        <v>17.21050849434463</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83083859092812</v>
+        <v>43.89887671326753</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93751025973452</v>
+        <v>99.92265044206817</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.14241659410298</v>
+        <v>80.34365363258826</v>
       </c>
       <c r="C18" t="n">
-        <v>35.53854098092543</v>
+        <v>36.72631541475617</v>
       </c>
       <c r="D18" t="n">
-        <v>1.266866101901424</v>
+        <v>1.337523845032655</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85059198693178</v>
+        <v>12.21113609036372</v>
       </c>
       <c r="F18" t="n">
-        <v>0.757829815814282</v>
+        <v>0.758369675165813</v>
       </c>
       <c r="G18" t="n">
-        <v>21.68667037169829</v>
+        <v>22.44880178441847</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27955030082772</v>
+        <v>36.91090890438232</v>
       </c>
       <c r="I18" t="n">
-        <v>1.564471668090221</v>
+        <v>1.937102863438953</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736436348839263</v>
+        <v>4.739810469786332</v>
       </c>
       <c r="K18" t="n">
-        <v>20.85758340589702</v>
+        <v>19.65634636741175</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55176089735502</v>
+        <v>43.55281997401115</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94788528417747</v>
+        <v>99.93548175617906</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.20253061196526</v>
+        <v>79.29991837829532</v>
       </c>
       <c r="C19" t="n">
-        <v>34.83215727023043</v>
+        <v>35.98113820505422</v>
       </c>
       <c r="D19" t="n">
-        <v>1.233038767847021</v>
+        <v>1.299624606688295</v>
       </c>
       <c r="E19" t="n">
-        <v>11.75273396412951</v>
+        <v>12.1343537275914</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758253433967806</v>
+        <v>0.7588846110864497</v>
       </c>
       <c r="G19" t="n">
-        <v>21.10760187970051</v>
+        <v>21.81270659065225</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30038914080615</v>
+        <v>36.93597155322051</v>
       </c>
       <c r="I19" t="n">
-        <v>1.311429463215479</v>
+        <v>1.615348469766084</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739083962298787</v>
+        <v>4.743028819290311</v>
       </c>
       <c r="K19" t="n">
-        <v>21.79746938803475</v>
+        <v>20.7000816217047</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32668344844232</v>
+        <v>43.26497176036778</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95631010670748</v>
+        <v>99.94619158712669</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.70716356721887</v>
+        <v>76.63785057336781</v>
       </c>
       <c r="C20" t="n">
-        <v>32.53840398190062</v>
+        <v>33.5678556852251</v>
       </c>
       <c r="D20" t="n">
-        <v>1.143340171584595</v>
+        <v>1.202172036124725</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08000064528775</v>
+        <v>11.44894255290552</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586184642291636</v>
+        <v>0.7593291916830321</v>
       </c>
       <c r="G20" t="n">
-        <v>19.5721089913616</v>
+        <v>20.17707710405405</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31834589535134</v>
+        <v>36.95760991039444</v>
       </c>
       <c r="I20" t="n">
-        <v>1.093383997972156</v>
+        <v>1.346912330187107</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741365401432272</v>
+        <v>4.745807448018952</v>
       </c>
       <c r="K20" t="n">
-        <v>24.29283643278112</v>
+        <v>23.36214942663218</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13233098911784</v>
+        <v>43.02512409731589</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96357140379958</v>
+        <v>99.95512920917318</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.61867882852469</v>
+        <v>82.47724664831971</v>
       </c>
       <c r="C21" t="n">
-        <v>36.2956819147872</v>
+        <v>37.04637616734158</v>
       </c>
       <c r="D21" t="n">
-        <v>1.144025012485441</v>
+        <v>1.203194758928711</v>
       </c>
       <c r="E21" t="n">
-        <v>13.08078520201997</v>
+        <v>13.36499591444572</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590728635106312</v>
+        <v>0.7599751751668682</v>
       </c>
       <c r="G21" t="n">
-        <v>21.333539319715</v>
+        <v>21.74972675120168</v>
       </c>
       <c r="H21" t="n">
-        <v>39.09040591132528</v>
+        <v>38.54453524608611</v>
       </c>
       <c r="I21" t="n">
-        <v>1.466645122526932</v>
+        <v>2.104973957697674</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744205396941445</v>
+        <v>4.749844844792928</v>
       </c>
       <c r="K21" t="n">
-        <v>18.38132117147529</v>
+        <v>17.52275335168032</v>
       </c>
       <c r="L21" t="n">
-        <v>45.274138008622</v>
+        <v>45.36076432374028</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95114109488449</v>
+        <v>99.92989384276218</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.81260608810479</v>
+        <v>45.32985302396663</v>
       </c>
       <c r="M2" t="n">
-        <v>98.67497568998047</v>
+        <v>100.5033354424085</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08835848083173</v>
+        <v>88.02123639029236</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94807634028534</v>
+        <v>45.89674198001491</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228872424516733</v>
+        <v>2.228739264529521</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720793964223981</v>
+        <v>5.687883145583098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429574748389109</v>
+        <v>0.742913088176507</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97920960077526</v>
+        <v>33.96207740372738</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1760438425899</v>
+        <v>34.17400205611932</v>
       </c>
       <c r="I3" t="n">
-        <v>6.596996956143755</v>
+        <v>6.582414631053389</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643484217743193</v>
+        <v>4.643206801103169</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91164151916827</v>
+        <v>11.97876360970762</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90349884569005</v>
+        <v>48.88822039704272</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632167051437</v>
+        <v>106.7637259867653</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.35208628472819</v>
+        <v>86.99905440022725</v>
       </c>
       <c r="C4" t="n">
-        <v>42.85181084549352</v>
+        <v>42.51365516626435</v>
       </c>
       <c r="D4" t="n">
-        <v>2.194336712077346</v>
+        <v>2.178919248784707</v>
       </c>
       <c r="E4" t="n">
-        <v>6.550327725400022</v>
+        <v>6.476889038780159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445193506206323</v>
+        <v>0.7444777479735264</v>
       </c>
       <c r="G4" t="n">
-        <v>33.45271189781926</v>
+        <v>33.20290774314464</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24789012854908</v>
+        <v>34.24597640678221</v>
       </c>
       <c r="I4" t="n">
-        <v>5.509054528882889</v>
+        <v>5.496898289927476</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653245941378952</v>
+        <v>4.65298592483454</v>
       </c>
       <c r="K4" t="n">
-        <v>12.64791371527181</v>
+        <v>13.00094559977275</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31702552378622</v>
+        <v>44.30255438310031</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81675008455156</v>
+        <v>99.81715514913741</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.43446431207759</v>
+        <v>85.89784778936564</v>
       </c>
       <c r="C5" t="n">
-        <v>42.78942017561153</v>
+        <v>42.26544526364467</v>
       </c>
       <c r="D5" t="n">
-        <v>2.150426035427566</v>
+        <v>2.125374948101124</v>
       </c>
       <c r="E5" t="n">
-        <v>7.185753231158263</v>
+        <v>7.082544969813044</v>
       </c>
       <c r="F5" t="n">
-        <v>0.74583983479465</v>
+        <v>0.7458034848180016</v>
       </c>
       <c r="G5" t="n">
-        <v>32.78329265731775</v>
+        <v>32.3869865121216</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3086324005539</v>
+        <v>34.30696030162807</v>
       </c>
       <c r="I5" t="n">
-        <v>4.599021185358906</v>
+        <v>4.588905792771265</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661498967466562</v>
+        <v>4.66127178011251</v>
       </c>
       <c r="K5" t="n">
-        <v>13.5655356879224</v>
+        <v>14.10215221063437</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49201484399711</v>
+        <v>43.47971090655631</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84697070753103</v>
+        <v>99.84730838083536</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.37838010080337</v>
+        <v>84.46063853849149</v>
       </c>
       <c r="C6" t="n">
-        <v>42.44798048983495</v>
+        <v>41.54084869075345</v>
       </c>
       <c r="D6" t="n">
-        <v>2.099648922989296</v>
+        <v>2.055039371101321</v>
       </c>
       <c r="E6" t="n">
-        <v>7.655789171849896</v>
+        <v>7.48647187531219</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469574978354222</v>
+        <v>0.7469307669667055</v>
       </c>
       <c r="G6" t="n">
-        <v>32.00919445076104</v>
+        <v>31.31519568027327</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36004490042941</v>
+        <v>34.35881528046845</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83826079546691</v>
+        <v>3.829868270827664</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668484361471388</v>
+        <v>4.668317293541909</v>
       </c>
       <c r="K6" t="n">
-        <v>14.62161989919663</v>
+        <v>15.53936146150848</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80264902248621</v>
+        <v>42.7923202423833</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8722494115178</v>
+        <v>99.87253039464524</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84.05930291085444</v>
+        <v>82.91648197177086</v>
       </c>
       <c r="C7" t="n">
-        <v>41.7256046306349</v>
+        <v>40.5914072756589</v>
       </c>
       <c r="D7" t="n">
-        <v>2.035916761394554</v>
+        <v>1.979910604516382</v>
       </c>
       <c r="E7" t="n">
-        <v>7.957176262587923</v>
+        <v>7.745388623439807</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479061200315651</v>
+        <v>0.7478903407913211</v>
       </c>
       <c r="G7" t="n">
-        <v>31.03759623216503</v>
+        <v>30.17036504592677</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40368152145199</v>
+        <v>34.40295567640077</v>
       </c>
       <c r="I7" t="n">
-        <v>3.20261276302611</v>
+        <v>3.195657050750067</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674413250197282</v>
+        <v>4.674314629945757</v>
       </c>
       <c r="K7" t="n">
-        <v>15.94069708914556</v>
+        <v>17.08351802822913</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22707992478989</v>
+        <v>42.21868946636675</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89338164457035</v>
+        <v>99.89361477025477</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.92716254395577</v>
+        <v>87.67303029307553</v>
       </c>
       <c r="C8" t="n">
-        <v>44.05058549541766</v>
+        <v>42.79874629088569</v>
       </c>
       <c r="D8" t="n">
-        <v>2.040208098899428</v>
+        <v>1.984142642001695</v>
       </c>
       <c r="E8" t="n">
-        <v>9.804204691191716</v>
+        <v>9.514143479877252</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494825683637736</v>
+        <v>0.7494889482991109</v>
       </c>
       <c r="G8" t="n">
-        <v>31.54954065680356</v>
+        <v>30.64245307762292</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47619814473358</v>
+        <v>34.4764916217591</v>
       </c>
       <c r="I8" t="n">
-        <v>5.623262331690123</v>
+        <v>5.622004596646004</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684266052273586</v>
+        <v>4.684305926869443</v>
       </c>
       <c r="K8" t="n">
-        <v>11.07283745604422</v>
+        <v>12.32696970692446</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68952923315461</v>
+        <v>44.68728356038844</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81295218461651</v>
+        <v>99.8129995581986</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.08542979775436</v>
+        <v>85.70424472287834</v>
       </c>
       <c r="C9" t="n">
-        <v>43.08271192623626</v>
+        <v>41.70227654936018</v>
       </c>
       <c r="D9" t="n">
-        <v>1.957127701140062</v>
+        <v>1.894897704871292</v>
       </c>
       <c r="E9" t="n">
-        <v>10.18737450301231</v>
+        <v>9.868465305092352</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508293015335434</v>
+        <v>0.7508571296690697</v>
       </c>
       <c r="G9" t="n">
-        <v>30.2647950525162</v>
+        <v>29.26418331992299</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53814787054299</v>
+        <v>34.5394279647772</v>
       </c>
       <c r="I9" t="n">
-        <v>4.694472234424615</v>
+        <v>4.693556238113758</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692683134584647</v>
+        <v>4.692857060431685</v>
       </c>
       <c r="K9" t="n">
-        <v>12.91457020224563</v>
+        <v>14.29575527712166</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84651614008227</v>
+        <v>43.84580137916687</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84379826856416</v>
+        <v>99.84383320564871</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.97457365831912</v>
+        <v>83.51160742085703</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70128045132583</v>
+        <v>40.23764896838352</v>
       </c>
       <c r="D10" t="n">
-        <v>1.862573049931242</v>
+        <v>1.796433141404562</v>
       </c>
       <c r="E10" t="n">
-        <v>10.34820433312144</v>
+        <v>10.00857238140815</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519832953266544</v>
+        <v>0.7520311849119441</v>
       </c>
       <c r="G10" t="n">
-        <v>28.80261292795166</v>
+        <v>27.74352865429168</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59123158502609</v>
+        <v>34.59343450594942</v>
       </c>
       <c r="I10" t="n">
-        <v>3.918072871170432</v>
+        <v>3.917412647191623</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699895595791591</v>
+        <v>4.70019490569965</v>
       </c>
       <c r="K10" t="n">
-        <v>15.02542634168089</v>
+        <v>16.48839257914298</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14289120048149</v>
+        <v>43.14358189030368</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86959799348821</v>
+        <v>99.86962343783017</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.6505728469383</v>
+        <v>81.20963128128173</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98554958261276</v>
+        <v>38.54267431232877</v>
       </c>
       <c r="D11" t="n">
-        <v>1.759348122996165</v>
+        <v>1.694139376469545</v>
       </c>
       <c r="E11" t="n">
-        <v>10.31959489077586</v>
+        <v>9.983472298888413</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752974822441235</v>
+        <v>0.7530402227583773</v>
       </c>
       <c r="G11" t="n">
-        <v>27.20635466836992</v>
+        <v>26.16373704767999</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6368418322968</v>
+        <v>34.63985024688535</v>
       </c>
       <c r="I11" t="n">
-        <v>3.269365869800597</v>
+        <v>3.268890696360194</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70609264025772</v>
+        <v>4.706501392239859</v>
       </c>
       <c r="K11" t="n">
-        <v>17.34942715306169</v>
+        <v>18.79036871871827</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55618790679304</v>
+        <v>42.55813995097542</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89116464246749</v>
+        <v>99.89118298202246</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.28165257967922</v>
+        <v>78.83524271556033</v>
       </c>
       <c r="C12" t="n">
-        <v>38.12343083035195</v>
+        <v>36.67401297679161</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65513098516872</v>
+        <v>1.589670101399266</v>
       </c>
       <c r="E12" t="n">
-        <v>10.16289390083878</v>
+        <v>9.822376607233702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538275626328653</v>
+        <v>0.7539085754855406</v>
       </c>
       <c r="G12" t="n">
-        <v>25.59475297499543</v>
+        <v>24.55034757071941</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67606788111179</v>
+        <v>34.67979447233486</v>
       </c>
       <c r="I12" t="n">
-        <v>2.727557008476207</v>
+        <v>2.72721679160291</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711422266455409</v>
+        <v>4.711928596784629</v>
       </c>
       <c r="K12" t="n">
-        <v>19.71834742032079</v>
+        <v>21.16475728443968</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06740603072169</v>
+        <v>42.07042721942537</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90918428139443</v>
+        <v>99.90919748065666</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.87716221675811</v>
+        <v>76.54215635344167</v>
       </c>
       <c r="C13" t="n">
-        <v>36.14094242300305</v>
+        <v>34.80199660266413</v>
       </c>
       <c r="D13" t="n">
-        <v>1.550265222737698</v>
+        <v>1.489781730699708</v>
       </c>
       <c r="E13" t="n">
-        <v>9.898189708365109</v>
+        <v>9.584333985659388</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545616638678626</v>
+        <v>0.7546554801962969</v>
       </c>
       <c r="G13" t="n">
-        <v>23.97312102622072</v>
+        <v>23.0077040896673</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70983653792167</v>
+        <v>34.71415208902965</v>
       </c>
       <c r="I13" t="n">
-        <v>2.275177658470916</v>
+        <v>2.274932226962458</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716010399174142</v>
+        <v>4.716596751226856</v>
       </c>
       <c r="K13" t="n">
-        <v>22.12283778324189</v>
+        <v>23.45784364655832</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66045432129737</v>
+        <v>41.66440372878859</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92423452754232</v>
+        <v>99.92424397801105</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.52482874768205</v>
+        <v>83.39918628242378</v>
       </c>
       <c r="C14" t="n">
-        <v>40.06323481317646</v>
+        <v>39.0908659897134</v>
       </c>
       <c r="D14" t="n">
-        <v>1.552257739693079</v>
+        <v>1.491507611853519</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12855229199481</v>
+        <v>11.96663745797964</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555314830233759</v>
+        <v>0.755529732876439</v>
       </c>
       <c r="G14" t="n">
-        <v>25.67838556796969</v>
+        <v>24.92247714232701</v>
       </c>
       <c r="H14" t="n">
-        <v>36.42890071046181</v>
+        <v>36.64248681825165</v>
       </c>
       <c r="I14" t="n">
-        <v>3.259129185643176</v>
+        <v>2.898486688657782</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722071768896099</v>
+        <v>4.722060830477743</v>
       </c>
       <c r="K14" t="n">
-        <v>15.47517125231796</v>
+        <v>16.60081371757623</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35309574498216</v>
+        <v>44.21181586812409</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89150181047658</v>
+        <v>99.90349557541371</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.75206567723824</v>
+        <v>82.67962412007311</v>
       </c>
       <c r="C15" t="n">
-        <v>39.7892114137261</v>
+        <v>38.81915737833286</v>
       </c>
       <c r="D15" t="n">
-        <v>1.522787351500838</v>
+        <v>1.464971330306658</v>
       </c>
       <c r="E15" t="n">
-        <v>12.35684761261368</v>
+        <v>12.15669203239641</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563490546586539</v>
+        <v>0.7562661858135007</v>
       </c>
       <c r="G15" t="n">
-        <v>25.19628388084782</v>
+        <v>24.47906682042318</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47373623861647</v>
+        <v>36.67820409827955</v>
       </c>
       <c r="I15" t="n">
-        <v>2.718879947384201</v>
+        <v>2.417759991519436</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727181591616587</v>
+        <v>4.72666366133438</v>
       </c>
       <c r="K15" t="n">
-        <v>16.24793432276175</v>
+        <v>17.32037587992689</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8723228972443</v>
+        <v>43.77995322261089</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90946863373215</v>
+        <v>99.91948648087063</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.25532418570592</v>
+        <v>80.23243143517414</v>
       </c>
       <c r="C16" t="n">
-        <v>37.71314862300315</v>
+        <v>36.74560368286291</v>
       </c>
       <c r="D16" t="n">
-        <v>1.426815595915087</v>
+        <v>1.372025362174081</v>
       </c>
       <c r="E16" t="n">
-        <v>11.95604637976836</v>
+        <v>11.72148487437596</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570527129730962</v>
+        <v>0.7568997623729216</v>
       </c>
       <c r="G16" t="n">
-        <v>23.60831981226093</v>
+        <v>22.92597802097888</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50766904729124</v>
+        <v>36.70893197001869</v>
       </c>
       <c r="I16" t="n">
-        <v>2.267841181415351</v>
+        <v>2.01648793042285</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731579456081851</v>
+        <v>4.73062351483076</v>
       </c>
       <c r="K16" t="n">
-        <v>18.74467581429407</v>
+        <v>19.76756856482587</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46665111971988</v>
+        <v>43.41966775254679</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9244755570171</v>
+        <v>99.93284000023556</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.78949150565538</v>
+        <v>81.89665087350515</v>
       </c>
       <c r="C17" t="n">
-        <v>38.81326523445603</v>
+        <v>37.96741348321744</v>
       </c>
       <c r="D17" t="n">
-        <v>1.428149904917313</v>
+        <v>1.373139714415101</v>
       </c>
       <c r="E17" t="n">
-        <v>12.69379535255929</v>
+        <v>12.49329155192992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577606827016103</v>
+        <v>0.757514512631686</v>
       </c>
       <c r="G17" t="n">
-        <v>23.96985612854035</v>
+        <v>23.37430465045703</v>
       </c>
       <c r="H17" t="n">
-        <v>36.88126839249776</v>
+        <v>37.16845304680403</v>
       </c>
       <c r="I17" t="n">
-        <v>2.322656777553992</v>
+        <v>1.995481693319347</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736004266885065</v>
+        <v>4.734465703948038</v>
       </c>
       <c r="K17" t="n">
-        <v>17.21050849434463</v>
+        <v>18.10334912649484</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89887671326753</v>
+        <v>43.86277531401473</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92265044206817</v>
+        <v>99.93353792372702</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.34365363258826</v>
+        <v>79.51509784011211</v>
       </c>
       <c r="C18" t="n">
-        <v>36.72631541475617</v>
+        <v>35.89384763122395</v>
       </c>
       <c r="D18" t="n">
-        <v>1.337523845032655</v>
+        <v>1.286223763508336</v>
       </c>
       <c r="E18" t="n">
-        <v>12.21113609036372</v>
+        <v>11.97984427847743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758369675165813</v>
+        <v>0.7580429450582531</v>
       </c>
       <c r="G18" t="n">
-        <v>22.44880178441847</v>
+        <v>21.89477573278656</v>
       </c>
       <c r="H18" t="n">
-        <v>36.91090890438232</v>
+        <v>37.1943812838315</v>
       </c>
       <c r="I18" t="n">
-        <v>1.937102863438953</v>
+        <v>1.664061429835937</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739810469786332</v>
+        <v>4.737768406614082</v>
       </c>
       <c r="K18" t="n">
-        <v>19.65634636741175</v>
+        <v>20.48490215988788</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55281997401115</v>
+        <v>43.56582016185153</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93548175617906</v>
+        <v>99.94456995296336</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.29991837829532</v>
+        <v>78.54534709281118</v>
       </c>
       <c r="C19" t="n">
-        <v>35.98113820505422</v>
+        <v>35.17978219500282</v>
       </c>
       <c r="D19" t="n">
-        <v>1.299624606688295</v>
+        <v>1.251465794527415</v>
       </c>
       <c r="E19" t="n">
-        <v>12.1343537275914</v>
+        <v>11.88744192562275</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588846110864497</v>
+        <v>0.7584894635024264</v>
       </c>
       <c r="G19" t="n">
-        <v>21.81270659065225</v>
+        <v>21.30310734867225</v>
       </c>
       <c r="H19" t="n">
-        <v>36.93597155322051</v>
+        <v>37.21629030280083</v>
       </c>
       <c r="I19" t="n">
-        <v>1.615348469766084</v>
+        <v>1.387993110795357</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743028819290311</v>
+        <v>4.740559146890165</v>
       </c>
       <c r="K19" t="n">
-        <v>20.7000816217047</v>
+        <v>21.4546529071888</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26497176036778</v>
+        <v>43.31932569757085</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94619158712669</v>
+        <v>99.95376079976248</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.63785057336781</v>
+        <v>76.00430914486327</v>
       </c>
       <c r="C20" t="n">
-        <v>33.5678556852251</v>
+        <v>32.8522434053207</v>
       </c>
       <c r="D20" t="n">
-        <v>1.202172036124725</v>
+        <v>1.159724364393861</v>
       </c>
       <c r="E20" t="n">
-        <v>11.44894255290552</v>
+        <v>11.20888172502023</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593291916830321</v>
+        <v>0.7588744243044099</v>
       </c>
       <c r="G20" t="n">
-        <v>20.17707710405405</v>
+        <v>19.74143659186676</v>
       </c>
       <c r="H20" t="n">
-        <v>36.95760991039444</v>
+        <v>37.23517891451029</v>
       </c>
       <c r="I20" t="n">
-        <v>1.346912330187107</v>
+        <v>1.157247972865154</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745807448018952</v>
+        <v>4.742965151902562</v>
       </c>
       <c r="K20" t="n">
-        <v>23.36214942663218</v>
+        <v>23.99569085513674</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02512409731589</v>
+        <v>43.11351037535379</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95512920917318</v>
+        <v>99.96144463581123</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.47724664831971</v>
+        <v>81.71969084981468</v>
       </c>
       <c r="C21" t="n">
-        <v>37.04637616734158</v>
+        <v>36.41883541530626</v>
       </c>
       <c r="D21" t="n">
-        <v>1.203194758928711</v>
+        <v>1.160495575628888</v>
       </c>
       <c r="E21" t="n">
-        <v>13.36499591444572</v>
+        <v>13.12833309576485</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599751751668682</v>
+        <v>0.7593790722190062</v>
       </c>
       <c r="G21" t="n">
-        <v>21.74972675120168</v>
+        <v>21.39484602555517</v>
       </c>
       <c r="H21" t="n">
-        <v>38.54453524608611</v>
+        <v>38.90022160437241</v>
       </c>
       <c r="I21" t="n">
-        <v>2.104973957697674</v>
+        <v>1.630296274905559</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749844844792928</v>
+        <v>4.746119201368789</v>
       </c>
       <c r="K21" t="n">
-        <v>17.52275335168032</v>
+        <v>18.28030915018533</v>
       </c>
       <c r="L21" t="n">
-        <v>45.36076432374028</v>
+        <v>45.24654833930718</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92989384276218</v>
+        <v>99.94569290479876</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_9_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32985302396663</v>
+        <v>43.65453017532507</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5033354424085</v>
+        <v>96.76294508584917</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02123639029236</v>
+        <v>81.39502257024574</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89674198001491</v>
+        <v>43.15057812580131</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228739264529521</v>
+        <v>2.175755061488091</v>
       </c>
       <c r="E3" t="n">
-        <v>5.687883145583098</v>
+        <v>4.143179364363841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742913088176507</v>
+        <v>0.7375751366242747</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96207740372738</v>
+        <v>32.72698238321671</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17400205611932</v>
+        <v>33.92845628471662</v>
       </c>
       <c r="I3" t="n">
-        <v>6.582414631053389</v>
+        <v>3.073229735934477</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643206801103169</v>
+        <v>4.609844603901716</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97876360970762</v>
+        <v>18.60497742975425</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88822039704272</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637259867653</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99905440022725</v>
+        <v>88.43317895865633</v>
       </c>
       <c r="C4" t="n">
-        <v>42.51365516626435</v>
+        <v>42.75139346519498</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178919248784707</v>
+        <v>2.181439352784315</v>
       </c>
       <c r="E4" t="n">
-        <v>6.476889038780159</v>
+        <v>6.522835585331984</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444777479735264</v>
+        <v>0.7395020961445051</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20290774314464</v>
+        <v>33.41930702427211</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24597640678221</v>
+        <v>34.01709642264723</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496898289927476</v>
+        <v>6.931110376573021</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65298592483454</v>
+        <v>4.621888100903156</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00094559977275</v>
+        <v>11.56682104134367</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30255438310031</v>
+        <v>45.45135050620834</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81715514913741</v>
+        <v>99.76956501274699</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.89784778936564</v>
+        <v>87.18189321411907</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26544526364467</v>
+        <v>42.57445253296413</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125374948101124</v>
+        <v>2.121324143329706</v>
       </c>
       <c r="E5" t="n">
-        <v>7.082544969813044</v>
+        <v>7.307866793673793</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458034848180016</v>
+        <v>0.741138813079523</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3869865121216</v>
+        <v>32.49835149139068</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30696030162807</v>
+        <v>34.09238540165805</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588905792771265</v>
+        <v>5.788708989240305</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66127178011251</v>
+        <v>4.632117581747018</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10215221063437</v>
+        <v>12.81810678588093</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47971090655631</v>
+        <v>44.41490983736124</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84730838083536</v>
+        <v>99.8074691562063</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.46063853849149</v>
+        <v>85.69341844930882</v>
       </c>
       <c r="C6" t="n">
-        <v>41.54084869075345</v>
+        <v>41.98419383628014</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055039371101321</v>
+        <v>2.049861173358606</v>
       </c>
       <c r="E6" t="n">
-        <v>7.48647187531219</v>
+        <v>7.86717887804704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469307669667055</v>
+        <v>0.7425321206401433</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31519568027327</v>
+        <v>31.4035500561446</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35881528046845</v>
+        <v>34.15647754944658</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829868270827664</v>
+        <v>4.832992917670948</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668317293541909</v>
+        <v>4.640825754000894</v>
       </c>
       <c r="K6" t="n">
-        <v>15.53936146150848</v>
+        <v>14.30658155069119</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7923202423833</v>
+        <v>43.54842714110532</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87253039464524</v>
+        <v>99.83920252807665</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.91648197177086</v>
+        <v>84.04804376099239</v>
       </c>
       <c r="C7" t="n">
-        <v>40.5914072756589</v>
+        <v>41.08899655621718</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979910604516382</v>
+        <v>1.971385147820002</v>
       </c>
       <c r="E7" t="n">
-        <v>7.745388623439807</v>
+        <v>8.238318017672936</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478903407913211</v>
+        <v>0.7437200634849965</v>
       </c>
       <c r="G7" t="n">
-        <v>30.17036504592677</v>
+        <v>30.20130971507264</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40295567640077</v>
+        <v>34.21112292030983</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195657050750067</v>
+        <v>4.033937499850756</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674314629945757</v>
+        <v>4.648250396781227</v>
       </c>
       <c r="K7" t="n">
-        <v>17.08351802822913</v>
+        <v>15.9519562390076</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21868946636675</v>
+        <v>42.8247974015066</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89361477025477</v>
+        <v>99.86575019673138</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.67303029307553</v>
+        <v>82.24848232541486</v>
       </c>
       <c r="C8" t="n">
-        <v>42.79874629088569</v>
+        <v>39.91544060567451</v>
       </c>
       <c r="D8" t="n">
-        <v>1.984142642001695</v>
+        <v>1.886166165497451</v>
       </c>
       <c r="E8" t="n">
-        <v>9.514143479877252</v>
+        <v>8.443225674448421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494889482991109</v>
+        <v>0.7447346763093394</v>
       </c>
       <c r="G8" t="n">
-        <v>30.64245307762292</v>
+        <v>28.8957683389632</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4764916217591</v>
+        <v>34.25779511022961</v>
       </c>
       <c r="I8" t="n">
-        <v>5.622004596646004</v>
+        <v>3.366200633033463</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684305926869443</v>
+        <v>4.654591726933369</v>
       </c>
       <c r="K8" t="n">
-        <v>12.32696970692446</v>
+        <v>17.75151767458516</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68728356038844</v>
+        <v>42.22098790030002</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8129995581986</v>
+        <v>99.88794618055969</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.70424472287834</v>
+        <v>80.33398284428056</v>
       </c>
       <c r="C9" t="n">
-        <v>41.70227654936018</v>
+        <v>38.52292323978324</v>
       </c>
       <c r="D9" t="n">
-        <v>1.894897704871292</v>
+        <v>1.796196972153907</v>
       </c>
       <c r="E9" t="n">
-        <v>9.868465305092352</v>
+        <v>8.508560668895772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508571296690697</v>
+        <v>0.7456025281107448</v>
       </c>
       <c r="G9" t="n">
-        <v>29.26418331992299</v>
+        <v>27.51745447878811</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5394279647772</v>
+        <v>34.29771629309425</v>
       </c>
       <c r="I9" t="n">
-        <v>4.693556238113758</v>
+        <v>2.80843610254563</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692857060431685</v>
+        <v>4.660015800692153</v>
       </c>
       <c r="K9" t="n">
-        <v>14.29575527712166</v>
+        <v>19.66601715571942</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84580137916687</v>
+        <v>41.71755403135753</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84383320564871</v>
+        <v>99.90649442686019</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.51160742085703</v>
+        <v>85.54618015431817</v>
       </c>
       <c r="C10" t="n">
-        <v>40.23764896838352</v>
+        <v>42.12877982041591</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796433141404562</v>
+        <v>1.798172980591426</v>
       </c>
       <c r="E10" t="n">
-        <v>10.00857238140815</v>
+        <v>10.53563712963703</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520311849119441</v>
+        <v>0.7464227704947499</v>
       </c>
       <c r="G10" t="n">
-        <v>27.74352865429168</v>
+        <v>29.0948930953082</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59343450594942</v>
+        <v>35.8826139214941</v>
       </c>
       <c r="I10" t="n">
-        <v>3.917412647191623</v>
+        <v>2.823297941200479</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70019490569965</v>
+        <v>4.665142315592185</v>
       </c>
       <c r="K10" t="n">
-        <v>16.48839257914298</v>
+        <v>14.45381984568183</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14358189030368</v>
+        <v>43.32339381973093</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86962343783017</v>
+        <v>99.90599348582867</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.20963128128173</v>
+        <v>85.21742230059702</v>
       </c>
       <c r="C11" t="n">
-        <v>38.54267431232877</v>
+        <v>42.1014626734687</v>
       </c>
       <c r="D11" t="n">
-        <v>1.694139376469545</v>
+        <v>1.773148889163343</v>
       </c>
       <c r="E11" t="n">
-        <v>9.983472298888413</v>
+        <v>10.86175606431148</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530402227583773</v>
+        <v>0.7471295232600013</v>
       </c>
       <c r="G11" t="n">
-        <v>26.16373704767999</v>
+        <v>28.75929210006291</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63985024688535</v>
+        <v>35.98588461403234</v>
       </c>
       <c r="I11" t="n">
-        <v>3.268890696360194</v>
+        <v>2.420651589391944</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706501392239859</v>
+        <v>4.669559520375006</v>
       </c>
       <c r="K11" t="n">
-        <v>18.79036871871827</v>
+        <v>14.78257769940297</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55813995097542</v>
+        <v>43.03534756859832</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89118298202246</v>
+        <v>99.91938794146998</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.83524271556033</v>
+        <v>83.18241638932606</v>
       </c>
       <c r="C12" t="n">
-        <v>36.67401297679161</v>
+        <v>40.44252227516455</v>
       </c>
       <c r="D12" t="n">
-        <v>1.589670101399266</v>
+        <v>1.687341971036704</v>
       </c>
       <c r="E12" t="n">
-        <v>9.822376607233702</v>
+        <v>10.67260329206372</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539085754855406</v>
+        <v>0.7477339523431431</v>
       </c>
       <c r="G12" t="n">
-        <v>24.55034757071941</v>
+        <v>27.36756113054767</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67979447233486</v>
+        <v>36.01499725724365</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72721679160291</v>
+        <v>2.018841583946558</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711928596784629</v>
+        <v>4.673337202144642</v>
       </c>
       <c r="K12" t="n">
-        <v>21.16475728443968</v>
+        <v>16.81758361067392</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07042721942537</v>
+        <v>42.67265379223396</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90919748065666</v>
+        <v>99.93275967807243</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.54215635344167</v>
+        <v>84.35207060416573</v>
       </c>
       <c r="C13" t="n">
-        <v>34.80199660266413</v>
+        <v>41.4255526457444</v>
       </c>
       <c r="D13" t="n">
-        <v>1.489781730699708</v>
+        <v>1.688580311782213</v>
       </c>
       <c r="E13" t="n">
-        <v>9.584333985659388</v>
+        <v>11.31070580637055</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546554801962969</v>
+        <v>0.7482827145003589</v>
       </c>
       <c r="G13" t="n">
-        <v>23.0077040896673</v>
+        <v>27.70838603778965</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71415208902965</v>
+        <v>36.36216852028291</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274932226962458</v>
+        <v>1.857180247812806</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716596751226856</v>
+        <v>4.676766965627241</v>
       </c>
       <c r="K13" t="n">
-        <v>23.45784364655832</v>
+        <v>15.64792939583428</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66440372878859</v>
+        <v>42.86465734967899</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92424397801105</v>
+        <v>99.93813939125766</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.39918628242378</v>
+        <v>82.17513342729181</v>
       </c>
       <c r="C14" t="n">
-        <v>39.0908659897134</v>
+        <v>39.53695939465396</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491507611853519</v>
+        <v>1.59928357019619</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96663745797964</v>
+        <v>10.97066850726408</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755529732876439</v>
+        <v>0.7487527704777673</v>
       </c>
       <c r="G14" t="n">
-        <v>24.92247714232701</v>
+        <v>26.24309086022669</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64248681825165</v>
+        <v>36.38501049475764</v>
       </c>
       <c r="I14" t="n">
-        <v>2.898486688657782</v>
+        <v>1.548622408883398</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722060830477743</v>
+        <v>4.679704815486044</v>
       </c>
       <c r="K14" t="n">
-        <v>16.60081371757623</v>
+        <v>17.8248665727082</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21181586812409</v>
+        <v>42.58658569242083</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90349557541371</v>
+        <v>99.94841165978298</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.67962412007311</v>
+        <v>81.11479681932005</v>
       </c>
       <c r="C15" t="n">
-        <v>38.81915737833286</v>
+        <v>38.68434749366426</v>
       </c>
       <c r="D15" t="n">
-        <v>1.464971330306658</v>
+        <v>1.554164650342052</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15669203239641</v>
+        <v>10.8895982621566</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562661858135007</v>
+        <v>0.7491568077842242</v>
       </c>
       <c r="G15" t="n">
-        <v>24.47906682042318</v>
+        <v>25.51230238003347</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67820409827955</v>
+        <v>36.41422482707892</v>
       </c>
       <c r="I15" t="n">
-        <v>2.417759991519436</v>
+        <v>1.313119843273375</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72666366133438</v>
+        <v>4.6822300486514</v>
       </c>
       <c r="K15" t="n">
-        <v>17.32037587992689</v>
+        <v>18.88520318067996</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77995322261089</v>
+        <v>42.38670227072663</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91948648087063</v>
+        <v>99.95625294507086</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.23243143517414</v>
+        <v>78.46972306715308</v>
       </c>
       <c r="C16" t="n">
-        <v>36.74560368286291</v>
+        <v>36.24252610415957</v>
       </c>
       <c r="D16" t="n">
-        <v>1.372025362174081</v>
+        <v>1.446530772855707</v>
       </c>
       <c r="E16" t="n">
-        <v>11.72148487437596</v>
+        <v>10.31790027192691</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568997623729216</v>
+        <v>0.7495052047761394</v>
       </c>
       <c r="G16" t="n">
-        <v>22.92597802097888</v>
+        <v>23.74544451966278</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70893197001869</v>
+        <v>36.43115934100291</v>
       </c>
       <c r="I16" t="n">
-        <v>2.01648793042285</v>
+        <v>1.09477542707776</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73062351483076</v>
+        <v>4.684407529850869</v>
       </c>
       <c r="K16" t="n">
-        <v>19.76756856482587</v>
+        <v>21.53027693284693</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41966775254679</v>
+        <v>42.19072141179146</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93284000023556</v>
+        <v>99.96352444879797</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.89665087350515</v>
+        <v>83.4491277881388</v>
       </c>
       <c r="C17" t="n">
-        <v>37.96741348321744</v>
+        <v>39.54947818375634</v>
       </c>
       <c r="D17" t="n">
-        <v>1.373139714415101</v>
+        <v>1.447223888591454</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49329155192992</v>
+        <v>12.0686442537528</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757514512631686</v>
+        <v>0.7498643356437318</v>
       </c>
       <c r="G17" t="n">
-        <v>23.37430465045703</v>
+        <v>25.30269612575537</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16845304680403</v>
+        <v>37.99448939957426</v>
       </c>
       <c r="I17" t="n">
-        <v>1.995481693319347</v>
+        <v>1.199557687047874</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734465703948038</v>
+        <v>4.686652097773322</v>
       </c>
       <c r="K17" t="n">
-        <v>18.10334912649484</v>
+        <v>16.55087221186119</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86277531401473</v>
+        <v>43.85968349819787</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93353792372702</v>
+        <v>99.96003389381539</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.51509784011211</v>
+        <v>84.94453570872457</v>
       </c>
       <c r="C18" t="n">
-        <v>35.89384763122395</v>
+        <v>40.28782126826267</v>
       </c>
       <c r="D18" t="n">
-        <v>1.286223763508336</v>
+        <v>1.448310458304944</v>
       </c>
       <c r="E18" t="n">
-        <v>11.97984427847743</v>
+        <v>12.66395387350191</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580429450582531</v>
+        <v>0.7504273306873875</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89477573278656</v>
+        <v>25.45537753544793</v>
       </c>
       <c r="H18" t="n">
-        <v>37.1943812838315</v>
+        <v>38.02301550516619</v>
       </c>
       <c r="I18" t="n">
-        <v>1.664061429835937</v>
+        <v>1.91328018882005</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737768406614082</v>
+        <v>4.690170816796171</v>
       </c>
       <c r="K18" t="n">
-        <v>20.48490215988788</v>
+        <v>15.05546429127541</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56582016185153</v>
+        <v>44.59298628100662</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94456995296336</v>
+        <v>99.93627184054471</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.54534709281118</v>
+        <v>81.93118875774056</v>
       </c>
       <c r="C19" t="n">
-        <v>35.17978219500282</v>
+        <v>37.57045560651648</v>
       </c>
       <c r="D19" t="n">
-        <v>1.251465794527415</v>
+        <v>1.338880193971925</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88744192562275</v>
+        <v>11.97300698666317</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584894635024264</v>
+        <v>0.7509144297205544</v>
       </c>
       <c r="G19" t="n">
-        <v>21.30310734867225</v>
+        <v>23.53204081131695</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21629030280083</v>
+        <v>38.04769607493393</v>
       </c>
       <c r="I19" t="n">
-        <v>1.387993110795357</v>
+        <v>1.595435075380566</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740559146890165</v>
+        <v>4.693215185753465</v>
       </c>
       <c r="K19" t="n">
-        <v>21.4546529071888</v>
+        <v>18.06881124225944</v>
       </c>
       <c r="L19" t="n">
-        <v>43.31932569757085</v>
+        <v>44.3075864793124</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95376079976248</v>
+        <v>99.94685332808832</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.00430914486327</v>
+        <v>78.83058407080308</v>
       </c>
       <c r="C20" t="n">
-        <v>32.8522434053207</v>
+        <v>34.71582593964908</v>
       </c>
       <c r="D20" t="n">
-        <v>1.159724364393861</v>
+        <v>1.226896335456407</v>
       </c>
       <c r="E20" t="n">
-        <v>11.20888172502023</v>
+        <v>11.19329825513431</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588744243044099</v>
+        <v>0.7513368225767358</v>
       </c>
       <c r="G20" t="n">
-        <v>19.74143659186676</v>
+        <v>21.56382233989547</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23517891451029</v>
+        <v>38.06909808078191</v>
       </c>
       <c r="I20" t="n">
-        <v>1.157247972865154</v>
+        <v>1.330277095853649</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742965151902562</v>
+        <v>4.695855141104598</v>
       </c>
       <c r="K20" t="n">
-        <v>23.99569085513674</v>
+        <v>21.16941592919693</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11351037535379</v>
+        <v>44.0704404901712</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96144463581123</v>
+        <v>99.9556823590172</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.71969084981468</v>
+        <v>75.84481441283133</v>
       </c>
       <c r="C21" t="n">
-        <v>36.41883541530626</v>
+        <v>31.93434480284863</v>
       </c>
       <c r="D21" t="n">
-        <v>1.160495575628888</v>
+        <v>1.11964910981181</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12833309576485</v>
+        <v>10.39970435058267</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593790722190062</v>
+        <v>0.7517030577374285</v>
       </c>
       <c r="G21" t="n">
-        <v>21.39484602555517</v>
+        <v>19.67885451220491</v>
       </c>
       <c r="H21" t="n">
-        <v>38.90022160437241</v>
+        <v>38.08765466131157</v>
       </c>
       <c r="I21" t="n">
-        <v>1.630296274905559</v>
+        <v>1.109104610324003</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746119201368789</v>
+        <v>4.698144110858927</v>
       </c>
       <c r="K21" t="n">
-        <v>18.28030915018533</v>
+        <v>24.15518558716867</v>
       </c>
       <c r="L21" t="n">
-        <v>45.24654833930718</v>
+        <v>43.87351746843122</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94569290479876</v>
+        <v>99.96304785844852</v>
       </c>
     </row>
   </sheetData>
